--- a/outputs/07_preliminary_association/preliminary_association_summary.xlsx
+++ b/outputs/07_preliminary_association/preliminary_association_summary.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ai_use_group_counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dmi_group_counts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="it_org_label_counts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="correlation_core_variables" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="correlation_core_variables_nume" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="correlation_pairwise_n" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="group_mean_h1_ai_scope" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="group_mean_h2_ai_itorg" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="group_mean_h2_ai_itorg_diff" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="group_mean_h3_ai_dmi" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="group_mean_h3_ai_dmi_pivot" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="group_mean_h4_low_dmi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crosstab_ai_itorg" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crosstab_ai_dmi_group" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ai_use_group_counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="dmi_group_counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="it_org_label_counts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="auxiliary_descriptive_stats" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="correlation_core_variables" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="correlation_core_variables_nume" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="correlation_pairwise_n" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="group_mean_h1_ai_scope" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="group_mean_h2_ai_itorg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="group_mean_h2_ai_itorg_diff" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="group_mean_h3_ai_dmi" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="group_mean_h3_ai_dmi_pivot" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="group_mean_h4_low_dmi" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="crosstab_ai_itorg" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="crosstab_ai_dmi_group" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,16 +31,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -58,21 +56,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,12 +431,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>AI 활용 범위 그룹</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -494,48 +483,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>AI 활용 범위 그룹</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>DMI 그룹</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>평균</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>표준편차</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>표준오차</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI 하한</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI 상한</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>No IT org 평균</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IT org 평균</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>차이(IT org - No IT org)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p-value</t>
         </is>
       </c>
     </row>
@@ -545,268 +519,55 @@
           <t>0</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+      <c r="B2" t="n">
+        <v>3.831</v>
       </c>
       <c r="C2" t="n">
-        <v>4545</v>
+        <v>3.961</v>
       </c>
       <c r="D2" t="n">
-        <v>3.812</v>
+        <v>0.13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.793</v>
       </c>
       <c r="C3" t="n">
-        <v>1869</v>
+        <v>4.213</v>
       </c>
       <c r="D3" t="n">
-        <v>4.005</v>
+        <v>0.42</v>
       </c>
       <c r="E3" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.975</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.876</v>
       </c>
       <c r="C4" t="n">
-        <v>725</v>
+        <v>4.273</v>
       </c>
       <c r="D4" t="n">
-        <v>4.101</v>
+        <v>0.396</v>
       </c>
       <c r="E4" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.052</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.557</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.653</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>527</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.994</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.926</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.063</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>812</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.187</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.294</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>411</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3.856</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.783</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1023</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.025</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.977</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.074</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2009</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4.175</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.244</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -820,28 +581,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>AI 활용 범위 그룹</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DMI 그룹</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>표준오차</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>95% CI 하한</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>95% CI 상한</t>
         </is>
       </c>
     </row>
@@ -851,46 +632,268 @@
           <t>0</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4545</v>
+      </c>
+      <c r="D2" t="n">
         <v>3.812</v>
       </c>
-      <c r="C2" t="n">
-        <v>4.005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4.101</v>
+      <c r="E2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.833</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.557</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>3.994</v>
+        <v>1869</v>
       </c>
       <c r="D3" t="n">
-        <v>4.24</v>
+        <v>4.005</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.035</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>725</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.101</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.052</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>282</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>527</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.994</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.926</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.063</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>812</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.187</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.294</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2+</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>411</v>
+      </c>
+      <c r="D8" t="n">
         <v>3.856</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E8" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.783</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D9" t="n">
         <v>4.025</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.977</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.074</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D10" t="n">
         <v>4.21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.175</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.244</v>
       </c>
     </row>
   </sheetData>
@@ -904,139 +907,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DMI 집단</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>AI 활용 범위 그룹</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>평균</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>표준편차</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>표준오차</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI 하한</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI 상한</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>0</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>3.812</v>
+      </c>
       <c r="C2" t="n">
-        <v>4545</v>
+        <v>4.005</v>
       </c>
       <c r="D2" t="n">
-        <v>3.812</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.833</v>
+        <v>4.101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>3.557</v>
+      </c>
       <c r="C3" t="n">
-        <v>282</v>
+        <v>3.994</v>
       </c>
       <c r="D3" t="n">
-        <v>3.557</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.653</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>2+</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>3.856</v>
+      </c>
       <c r="C4" t="n">
-        <v>411</v>
+        <v>4.025</v>
       </c>
       <c r="D4" t="n">
-        <v>3.856</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.783</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
     </row>
   </sheetData>
@@ -1050,75 +991,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ai_use_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>No IT org</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>IT org</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DMI 집단</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AI 활용 범위 그룹</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>표준오차</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>95% CI 하한</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>95% CI 상한</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3802 (53.3%)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3337 (46.7%)</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4545</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.812</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.833</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>662 (40.8%)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>959 (59.2%)</t>
-        </is>
+      <c r="C3" t="n">
+        <v>282</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.653</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>2+</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1389 (40.3%)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2054 (59.7%)</t>
-        </is>
+      <c r="C4" t="n">
+        <v>411</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.856</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.783</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.93</v>
       </c>
     </row>
   </sheetData>
@@ -1132,26 +1137,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ai_use_group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>No IT org</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IT org</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3802 (53.3%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3337 (46.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>662 (40.8%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>959 (59.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1389 (40.3%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2054 (59.7%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ai_use_group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1238,12 +1325,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DMI 그룹</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1294,12 +1381,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>IT 조직 보유 여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1336,446 +1423,172 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>변수</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>프로세스 개선의 정도 (프로세스 개선 관련 정보화 효과 인식)
-(effect_proc_improve)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>정보화 효과 평균
-(effect_average)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>AI 활용 범위 (AI 이용 유형의 개수)
-(ai_use_sum)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>AI 실제 업무 이용 여부
-(ai_use)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>정보화 전담 인력 보유 여부
-(it_org_any)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>디지털 성숙도 (Digital Maturity Index, DMI) - 기업이 활용하고 있는 디지털 시스템 및 기술 유형의 개수
-(dmi)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>정보화 투자 범위 (정보화 투자 종류 개수)
-(it_invest_sum)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>기업 규모
-(firm_size)</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>변수명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>라벨</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>통계량</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>유효 N</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>값</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>프로세스 개선의 정도 (프로세스 개선 관련 정보화 효과 인식)
-(effect_proc_improve)</t>
+          <t>it_org_any</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.000***</t>
+          <t>정보화 전담 인력 보유 여부</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.725***</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.129***</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.128***</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.171***</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.235***</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.291***</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.169***</t>
-        </is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>정보화 효과 평균
-(effect_average)</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.725***</t>
+          <t>업종</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.000***</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.161***</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.159***</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.266***</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.357***</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.406***</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.204***</t>
-        </is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI 활용 범위 (AI 이용 유형의 개수)
-(ai_use_sum)</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.129***</t>
+          <t>지역</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.161***</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.000***</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.823***</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.119***</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.572***</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.400***</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.283***</t>
-        </is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI 실제 업무 이용 여부
-(ai_use)</t>
+          <t>firm_type</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.128***</t>
+          <t>조직 형태</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.159***</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.823***</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.000***</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.126***</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.566***</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.407***</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.314***</t>
-        </is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.343</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>정보화 전담 인력 보유 여부
-(it_org_any)</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.171***</t>
+          <t>표본 가중치</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.266***</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.119***</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.126***</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.000***</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.265***</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.492***</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.263***</t>
-        </is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.477</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>디지털 성숙도 (Digital Maturity Index, DMI) - 기업이 활용하고 있는 디지털 시스템 및 기술 유형의 개수
-(dmi)</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.235***</t>
+          <t>표본 가중치</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.357***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.572***</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.566***</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.265***</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.000***</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.575***</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.363***</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>정보화 투자 범위 (정보화 투자 종류 개수)
-(it_invest_sum)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.291***</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.406***</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.400***</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.407***</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.492***</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.575***</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.000***</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.382***</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>기업 규모
-(firm_size)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.169***</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.204***</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.283***</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.314***</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.263***</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.363***</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.382***</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.000***</t>
-        </is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.085</v>
       </c>
     </row>
   </sheetData>
@@ -1793,54 +1606,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>변수</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>프로세스 개선의 정도 (프로세스 개선 관련 정보화 효과 인식)
 (effect_proc_improve)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>정보화 효과 평균
 (effect_average)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AI 활용 범위 (AI 이용 유형의 개수)
 (ai_use_sum)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AI 실제 업무 이용 여부
 (ai_use)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>정보화 전담 인력 보유 여부
 (it_org_any)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>디지털 성숙도 (Digital Maturity Index, DMI) - 기업이 활용하고 있는 디지털 시스템 및 기술 유형의 개수
 (dmi)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>정보화 투자 범위 (정보화 투자 종류 개수)
 (it_invest_sum)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>기업 규모
 (firm_size)</t>
@@ -1854,29 +1667,45 @@
 (effect_proc_improve)</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.169</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.725***</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.129***</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.128***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.171***</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.235***</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.291***</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.169***</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1886,29 +1715,45 @@
 (effect_average)</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.204</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.725***</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.161***</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.159***</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.266***</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.357***</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.406***</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.204***</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1918,29 +1763,45 @@
 (ai_use_sum)</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.572</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.283</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.129***</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.161***</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.823***</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.572***</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.400***</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.283***</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1950,29 +1811,45 @@
 (ai_use)</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.314</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.128***</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.159***</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.823***</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.126***</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.566***</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.407***</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.314***</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1982,29 +1859,45 @@
 (it_org_any)</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.263</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.171***</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.266***</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.126***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.265***</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.492***</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.263***</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2014,29 +1907,45 @@
 (dmi)</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.572</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.363</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.235***</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.357***</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.572***</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.566***</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.265***</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.575***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.363***</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2046,29 +1955,45 @@
 (it_invest_sum)</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.382</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.291***</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.406***</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.400***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.407***</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.492***</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.575***</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.382***</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2078,29 +2003,45 @@
 (firm_size)</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.169***</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.204***</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.283***</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.314***</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.263***</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.363***</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.382***</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.000***</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2118,54 +2059,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>변수</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>프로세스 개선의 정도 (프로세스 개선 관련 정보화 효과 인식)
 (effect_proc_improve)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>정보화 효과 평균
 (effect_average)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AI 활용 범위 (AI 이용 유형의 개수)
 (ai_use_sum)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AI 실제 업무 이용 여부
 (ai_use)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>정보화 전담 인력 보유 여부
 (it_org_any)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>디지털 성숙도 (Digital Maturity Index, DMI) - 기업이 활용하고 있는 디지털 시스템 및 기술 유형의 개수
 (dmi)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>정보화 투자 범위 (정보화 투자 종류 개수)
 (it_invest_sum)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>기업 규모
 (firm_size)</t>
@@ -2180,28 +2121,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12203</v>
+        <v>0.725</v>
       </c>
       <c r="D2" t="n">
-        <v>12203</v>
+        <v>0.129</v>
       </c>
       <c r="E2" t="n">
-        <v>12203</v>
+        <v>0.128</v>
       </c>
       <c r="F2" t="n">
-        <v>12203</v>
+        <v>0.171</v>
       </c>
       <c r="G2" t="n">
-        <v>12203</v>
+        <v>0.235</v>
       </c>
       <c r="H2" t="n">
-        <v>12203</v>
+        <v>0.291</v>
       </c>
       <c r="I2" t="n">
-        <v>12203</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="3">
@@ -2212,28 +2153,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12203</v>
+        <v>0.725</v>
       </c>
       <c r="C3" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>12203</v>
+        <v>0.161</v>
       </c>
       <c r="E3" t="n">
-        <v>12203</v>
+        <v>0.159</v>
       </c>
       <c r="F3" t="n">
-        <v>12203</v>
+        <v>0.266</v>
       </c>
       <c r="G3" t="n">
-        <v>12203</v>
+        <v>0.357</v>
       </c>
       <c r="H3" t="n">
-        <v>12203</v>
+        <v>0.406</v>
       </c>
       <c r="I3" t="n">
-        <v>12203</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="4">
@@ -2244,28 +2185,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12203</v>
+        <v>0.129</v>
       </c>
       <c r="C4" t="n">
-        <v>12203</v>
+        <v>0.161</v>
       </c>
       <c r="D4" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>12203</v>
+        <v>0.823</v>
       </c>
       <c r="F4" t="n">
-        <v>12203</v>
+        <v>0.119</v>
       </c>
       <c r="G4" t="n">
-        <v>12203</v>
+        <v>0.572</v>
       </c>
       <c r="H4" t="n">
-        <v>12203</v>
+        <v>0.4</v>
       </c>
       <c r="I4" t="n">
-        <v>12203</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="5">
@@ -2276,28 +2217,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12203</v>
+        <v>0.128</v>
       </c>
       <c r="C5" t="n">
-        <v>12203</v>
+        <v>0.159</v>
       </c>
       <c r="D5" t="n">
-        <v>12203</v>
+        <v>0.823</v>
       </c>
       <c r="E5" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>12203</v>
+        <v>0.126</v>
       </c>
       <c r="G5" t="n">
-        <v>12203</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>12203</v>
+        <v>0.407</v>
       </c>
       <c r="I5" t="n">
-        <v>12203</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="6">
@@ -2308,28 +2249,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12203</v>
+        <v>0.171</v>
       </c>
       <c r="C6" t="n">
-        <v>12203</v>
+        <v>0.266</v>
       </c>
       <c r="D6" t="n">
-        <v>12203</v>
+        <v>0.119</v>
       </c>
       <c r="E6" t="n">
-        <v>12203</v>
+        <v>0.126</v>
       </c>
       <c r="F6" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>12203</v>
+        <v>0.265</v>
       </c>
       <c r="H6" t="n">
-        <v>12203</v>
+        <v>0.492</v>
       </c>
       <c r="I6" t="n">
-        <v>12203</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="7">
@@ -2340,28 +2281,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12203</v>
+        <v>0.235</v>
       </c>
       <c r="C7" t="n">
-        <v>12203</v>
+        <v>0.357</v>
       </c>
       <c r="D7" t="n">
-        <v>12203</v>
+        <v>0.572</v>
       </c>
       <c r="E7" t="n">
-        <v>12203</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>12203</v>
+        <v>0.265</v>
       </c>
       <c r="G7" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>12203</v>
+        <v>0.575</v>
       </c>
       <c r="I7" t="n">
-        <v>12203</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="8">
@@ -2372,28 +2313,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12203</v>
+        <v>0.291</v>
       </c>
       <c r="C8" t="n">
-        <v>12203</v>
+        <v>0.406</v>
       </c>
       <c r="D8" t="n">
-        <v>12203</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>12203</v>
+        <v>0.407</v>
       </c>
       <c r="F8" t="n">
-        <v>12203</v>
+        <v>0.492</v>
       </c>
       <c r="G8" t="n">
-        <v>12203</v>
+        <v>0.575</v>
       </c>
       <c r="H8" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>12203</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="9">
@@ -2404,28 +2345,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12203</v>
+        <v>0.169</v>
       </c>
       <c r="C9" t="n">
-        <v>12203</v>
+        <v>0.204</v>
       </c>
       <c r="D9" t="n">
-        <v>12203</v>
+        <v>0.283</v>
       </c>
       <c r="E9" t="n">
-        <v>12203</v>
+        <v>0.314</v>
       </c>
       <c r="F9" t="n">
-        <v>12203</v>
+        <v>0.263</v>
       </c>
       <c r="G9" t="n">
-        <v>12203</v>
+        <v>0.363</v>
       </c>
       <c r="H9" t="n">
-        <v>12203</v>
+        <v>0.382</v>
       </c>
       <c r="I9" t="n">
-        <v>12203</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2439,159 +2380,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>비교 기준</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>결과변수</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>집단</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>평균</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>표준편차</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>표준오차</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI 하한</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI 상한</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>프로세스 개선의 정도 (프로세스 개선 관련 정보화 효과 인식)
+(effect_proc_improve)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>정보화 효과 평균
+(effect_average)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AI 활용 범위 (AI 이용 유형의 개수)
+(ai_use_sum)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>AI 실제 업무 이용 여부
+(ai_use)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>정보화 전담 인력 보유 여부
+(it_org_any)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>디지털 성숙도 (Digital Maturity Index, DMI) - 기업이 활용하고 있는 디지털 시스템 및 기술 유형의 개수
+(dmi)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>정보화 투자 범위 (정보화 투자 종류 개수)
+(it_invest_sum)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>기업 규모
+(firm_size)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI 활용 범위 그룹</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>effect_proc_improve</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>프로세스 개선의 정도 (프로세스 개선 관련 정보화 효과 인식)
+(effect_proc_improve)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12203</v>
       </c>
       <c r="D2" t="n">
-        <v>7139</v>
+        <v>12203</v>
       </c>
       <c r="E2" t="n">
-        <v>3.892</v>
+        <v>12203</v>
       </c>
       <c r="F2" t="n">
-        <v>0.72</v>
+        <v>12203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008999999999999999</v>
+        <v>12203</v>
       </c>
       <c r="H2" t="n">
-        <v>3.875</v>
+        <v>12203</v>
       </c>
       <c r="I2" t="n">
-        <v>3.908</v>
+        <v>12203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI 활용 범위 그룹</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>effect_proc_improve</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>정보화 효과 평균
+(effect_average)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12203</v>
       </c>
       <c r="D3" t="n">
-        <v>1621</v>
+        <v>12203</v>
       </c>
       <c r="E3" t="n">
-        <v>4.041</v>
+        <v>12203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.832</v>
+        <v>12203</v>
       </c>
       <c r="G3" t="n">
-        <v>0.021</v>
+        <v>12203</v>
       </c>
       <c r="H3" t="n">
-        <v>4.001</v>
+        <v>12203</v>
       </c>
       <c r="I3" t="n">
-        <v>4.082</v>
+        <v>12203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI 활용 범위 그룹</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>effect_proc_improve</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
+          <t>AI 활용 범위 (AI 이용 유형의 개수)
+(ai_use_sum)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12203</v>
       </c>
       <c r="D4" t="n">
-        <v>3443</v>
+        <v>12203</v>
       </c>
       <c r="E4" t="n">
-        <v>4.113</v>
+        <v>12203</v>
       </c>
       <c r="F4" t="n">
-        <v>0.798</v>
+        <v>12203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.014</v>
+        <v>12203</v>
       </c>
       <c r="H4" t="n">
-        <v>4.086</v>
+        <v>12203</v>
       </c>
       <c r="I4" t="n">
-        <v>4.139</v>
+        <v>12203</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI 실제 업무 이용 여부
+(ai_use)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12203</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>정보화 전담 인력 보유 여부
+(it_org_any)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12203</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12203</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>디지털 성숙도 (Digital Maturity Index, DMI) - 기업이 활용하고 있는 디지털 시스템 및 기술 유형의 개수
+(dmi)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12203</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12203</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>정보화 투자 범위 (정보화 투자 종류 개수)
+(it_invest_sum)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12203</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12203</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>기업 규모
+(firm_size)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12203</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12203</v>
       </c>
     </row>
   </sheetData>
@@ -2605,46 +2705,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AI 활용 범위 그룹</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>IT 조직 보유 여부</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>비교 기준</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>결과변수</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>집단</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>평균</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>표준편차</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>표준오차</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>95% CI 하한</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>95% CI 상한</t>
         </is>
@@ -2653,181 +2758,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AI 활용 범위 그룹</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>effect_proc_improve</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>No IT org</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3802</v>
-      </c>
       <c r="D2" t="n">
-        <v>3.831</v>
+        <v>7139</v>
       </c>
       <c r="E2" t="n">
-        <v>0.741</v>
+        <v>3.892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.012</v>
+        <v>0.72</v>
       </c>
       <c r="G2" t="n">
-        <v>3.808</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>3.855</v>
+        <v>3.875</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.908</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>AI 활용 범위 그룹</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IT org</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3337</v>
+          <t>effect_proc_improve</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>3.961</v>
+        <v>1621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6879999999999999</v>
+        <v>4.041</v>
       </c>
       <c r="F3" t="n">
-        <v>0.012</v>
+        <v>0.832</v>
       </c>
       <c r="G3" t="n">
-        <v>3.937</v>
+        <v>0.021</v>
       </c>
       <c r="H3" t="n">
-        <v>3.984</v>
+        <v>4.001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.082</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>AI 활용 범위 그룹</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>No IT org</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>662</v>
+          <t>effect_proc_improve</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>3.793</v>
+        <v>3443</v>
       </c>
       <c r="E4" t="n">
-        <v>0.855</v>
+        <v>4.113</v>
       </c>
       <c r="F4" t="n">
-        <v>0.033</v>
+        <v>0.798</v>
       </c>
       <c r="G4" t="n">
-        <v>3.728</v>
+        <v>0.014</v>
       </c>
       <c r="H4" t="n">
-        <v>3.858</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT org</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>959</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.213</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.164</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.261</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>No IT org</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1389</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.876</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.834</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.918</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT org</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2054</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.273</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.305</v>
+        <v>4.086</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.139</v>
       </c>
     </row>
   </sheetData>
@@ -2841,33 +2871,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>AI 활용 범위 그룹</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>No IT org 평균</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>IT org 평균</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>차이(IT org - No IT org)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p-value</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>IT 조직 보유 여부</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>표준편차</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>표준오차</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>95% CI 하한</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>95% CI 상한</t>
         </is>
       </c>
     </row>
@@ -2877,55 +2922,178 @@
           <t>0</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>No IT org</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3802</v>
+      </c>
+      <c r="D2" t="n">
         <v>3.831</v>
       </c>
-      <c r="C2" t="n">
-        <v>3.961</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.13</v>
-      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.741</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.855</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.793</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IT org</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>4.213</v>
+        <v>3337</v>
       </c>
       <c r="D3" t="n">
-        <v>0.42</v>
+        <v>3.961</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.937</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.984</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>No IT org</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>662</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.793</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.728</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.858</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IT org</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>959</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.213</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.164</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.261</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2+</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>No IT org</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1389</v>
+      </c>
+      <c r="D6" t="n">
         <v>3.876</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E6" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.834</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.918</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IT org</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2054</v>
+      </c>
+      <c r="D7" t="n">
         <v>4.273</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+      <c r="E7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.305</v>
       </c>
     </row>
   </sheetData>
